--- a/docs/STAFF-DATA/013.xlsx
+++ b/docs/STAFF-DATA/013.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Velammal-Engineering-College-Backend\docs\STAFF-DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\VEC_Web_Engine\docs\STAFF-DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9780"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9780"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -465,10 +465,10 @@
     <t>https://www.linkedin.com/in/satishchennai/?originalSubdomain=in</t>
   </si>
   <si>
-    <t>https://www.scopus.com/authid/detail.uri?authorId=13806246500</t>
-  </si>
-  <si>
     <t>https://www.researchgate.net/profile/S-Satishkumar</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/results/results.uri?sort=plf-f&amp;src=s&amp;st1=satish+Kumar&amp;st2=s&amp;nlo=1&amp;nlr=20&amp;nls=count-f&amp;sid=ca5287c422edd6e5dec91a734cd442d3&amp;sot=anl&amp;sdt=aut&amp;sl=37&amp;s=AU-ID%28%22Satish+Kumar%2C+S.%22+13806246500%29&amp;txGid=5b7b5fd8edbb8c1267c2088b4cd16803&amp;sessionSearchId=ca5287c422edd6e5dec91a734cd442d3&amp;limit=10</t>
   </si>
 </sst>
 </file>
@@ -991,12 +991,12 @@
         <v>146</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>147</v>
@@ -1716,8 +1716,8 @@
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
-    <hyperlink ref="H3" r:id="rId3"/>
-    <hyperlink ref="E3" r:id="rId4"/>
+    <hyperlink ref="H3"/>
+    <hyperlink ref="E3" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
